--- a/Topography/Experimental_reach_down/Experimental Reach Surveying.xlsx
+++ b/Topography/Experimental_reach_down/Experimental Reach Surveying.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nicol\Documents\GitHub\La_Jara\Topography\Experimental_reach_down\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\huck4481\Documents\GitHub\La_Jara\Topography\Experimental_reach_down\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15B0EE7A-DC86-4F6E-8E43-6AC8FA7BFF7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82877091-8C33-4F2F-9AB5-C67FDC3F0C53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6875A78A-EB74-4CCE-9079-1EDDD22DA4D6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{6875A78A-EB74-4CCE-9079-1EDDD22DA4D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Long Profile" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="59">
   <si>
     <t>Point</t>
   </si>
@@ -206,12 +206,24 @@
   </si>
   <si>
     <t>Pressure Transducer Cross Section: 3,1m -&gt; at 35,2m</t>
+  </si>
+  <si>
+    <t>water height at rebar</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>cm</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -229,12 +241,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="15">
@@ -429,7 +447,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -447,10 +465,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -461,16 +475,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
@@ -479,7 +490,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -495,15 +506,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -516,13 +518,16 @@
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -542,10 +547,2474 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-2.6855424321959757E-2"/>
+                  <c:y val="-0.43258967629046369"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Long Profile'!$A$3:$A$51</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="49"/>
+                <c:pt idx="0">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>30.2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>30.4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>30.6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>30.8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>31.2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>31.4</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>31.6</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>31.8</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>32.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>32.4</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>32.6</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>32.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>33.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>33.4</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>33.6</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>33.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>34.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>34.4</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>34.6</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>34.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>35.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>35.4</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>35.6</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>35.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>36.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>36.4</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>36.6</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>36.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>37.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>37.4</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>37.6</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>37.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>38.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>38.4</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>38.6</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>38.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>39.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>39.4</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>39.6</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Long Profile'!$G$3:$G$51</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="49"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.77700000000000014</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.78500000000000014</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.66999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.68300000000000027</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.69500000000000028</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.74699999999999989</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.6120000000000001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.49400000000000022</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.49000000000000021</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.54899999999999993</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.55500000000000016</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.56600000000000028</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.60000000000000009</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.50600000000000023</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.51000000000000023</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.50499999999999989</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.45500000000000007</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.43800000000000017</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.39000000000000012</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.41999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.53200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.49500000000000011</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.36399999999999988</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.33400000000000007</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.39500000000000002</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.40300000000000002</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.37199999999999989</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.35499999999999998</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.36399999999999988</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.33800000000000008</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.32299999999999995</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.29800000000000004</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.28400000000000025</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.23499999999999988</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.16500000000000004</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.20599999999999996</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>7.1000000000000174E-2</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>4.4000000000000039E-2</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>3.0000000000000249E-2</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>6.3000000000000167E-2</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>7.0000000000000284E-2</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>3.4000000000000252E-2</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.14000000000000012</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>8.7000000000000188E-2</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>4.4999999999999929E-2</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>6.4999999999999947E-2</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>4.8000000000000043E-2</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>4.0000000000000036E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-877C-47E9-A497-57E507C7BB80}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="952242768"/>
+        <c:axId val="952243728"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="952242768"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="29"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="952243728"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="952243728"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="952242768"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>cross section</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Pressure Transducer XS'!$A$3:$A$34</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="32"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>110</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>130</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>190</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>210</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>220</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>230</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>240</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>260</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>270</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>280</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>290</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>310</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Pressure Transducer XS'!$G$3:$G$34</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="32"/>
+                <c:pt idx="0">
+                  <c:v>2756</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2755.9790000000003</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2756.0010000000002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2755.922</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2755.88</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2755.7930000000001</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2755.7400000000002</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2755.65</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2755.623</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2755.6280000000002</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2755.527</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2755.4960000000001</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2755.4830000000002</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2755.4870000000001</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2755.4470000000001</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2755.4830000000002</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2755.433</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2755.46</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2755.4680000000003</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2755.5140000000001</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2755.518</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2755.5230000000001</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2755.5460000000003</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2755.5350000000003</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2755.5650000000001</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2755.5860000000002</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2755.5980000000004</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2755.6030000000001</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2755.616</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>2755.7570000000001</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2755.7930000000001</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2755.8830000000003</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-29D1-44CF-8AAF-E9A471A2B0FB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>water</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Pressure Transducer XS'!$I$25:$I$34</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>130</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>230</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Pressure Transducer XS'!$J$25:$J$34</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>2755.527</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2755.5280000000002</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2755.5290000000005</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2755.5300000000007</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2755.5310000000009</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2755.5320000000011</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2755.5350000000003</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-29D1-44CF-8AAF-E9A471A2B0FB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>pressure sensor</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="triangle"/>
+            <c:size val="10"/>
+            <c:spPr>
+              <a:gradFill>
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="5000"/>
+                      <a:lumOff val="95000"/>
+                      <a:alpha val="98000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="86000">
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="45000"/>
+                      <a:lumOff val="55000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="61000">
+                    <a:schemeClr val="accent4">
+                      <a:alpha val="98000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="30000"/>
+                      <a:lumOff val="70000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="1"/>
+              </a:gradFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Pressure Transducer XS'!$A$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>130</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Pressure Transducer XS'!$G$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2755.4870000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-29D1-44CF-8AAF-E9A471A2B0FB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="495206448"/>
+        <c:axId val="495207888"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="495206448"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="495207888"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="495207888"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="495206448"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EBA63DEF-BF0F-48AF-98D3-04B1CFC12C29}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>114299</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>176211</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C4699EE-9298-5E8E-4D2D-3F9E3A0D0D37}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -583,7 +3052,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -689,7 +3158,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -831,7 +3300,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -855,11 +3324,10 @@
       <c r="A1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C1" s="7"/>
-      <c r="D1" s="8"/>
       <c r="E1" s="5" t="s">
         <v>7</v>
       </c>
@@ -877,722 +3345,872 @@
       <c r="D2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="26" t="s">
+      <c r="F2" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="G2" s="27" t="s">
+      <c r="G2" s="4" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="13">
+      <c r="A3" s="11">
         <v>30</v>
       </c>
-      <c r="B3" s="13">
+      <c r="B3" s="11">
         <v>1.85</v>
       </c>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="14" t="s">
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
+      <c r="F3" s="11">
+        <f>B3+G3</f>
+        <v>2.85</v>
+      </c>
+      <c r="G3" s="11">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="15">
+      <c r="A4" s="10">
         <v>30.2</v>
       </c>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15">
+      <c r="B4" s="10"/>
+      <c r="C4" s="10">
         <v>2.073</v>
       </c>
-      <c r="D4" s="15"/>
-      <c r="E4" s="16" t="s">
+      <c r="D4" s="10"/>
+      <c r="E4" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10">
+        <f>$F$3-C4</f>
+        <v>0.77700000000000014</v>
+      </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="15">
+      <c r="A5" s="10">
         <v>30.4</v>
       </c>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15">
+      <c r="B5" s="10"/>
+      <c r="C5" s="10">
         <v>2.0649999999999999</v>
       </c>
-      <c r="D5" s="15"/>
-      <c r="E5" s="16" t="s">
+      <c r="D5" s="10"/>
+      <c r="E5" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10">
+        <f t="shared" ref="G5:G51" si="0">$F$3-C5</f>
+        <v>0.78500000000000014</v>
+      </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="15">
+      <c r="A6" s="10">
         <v>30.6</v>
       </c>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15">
+      <c r="B6" s="10"/>
+      <c r="C6" s="10">
         <v>2.1800000000000002</v>
       </c>
-      <c r="D6" s="15"/>
-      <c r="E6" s="16" t="s">
+      <c r="D6" s="10"/>
+      <c r="E6" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10">
+        <f t="shared" si="0"/>
+        <v>0.66999999999999993</v>
+      </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="15">
+      <c r="A7" s="10">
         <v>30.8</v>
       </c>
-      <c r="B7" s="15"/>
-      <c r="C7" s="15">
+      <c r="B7" s="10"/>
+      <c r="C7" s="10">
         <v>2.1669999999999998</v>
       </c>
-      <c r="D7" s="15"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10">
+        <f t="shared" si="0"/>
+        <v>0.68300000000000027</v>
+      </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="15">
+      <c r="A8" s="10">
         <v>31</v>
       </c>
-      <c r="B8" s="15"/>
-      <c r="C8" s="15">
+      <c r="B8" s="10"/>
+      <c r="C8" s="10">
         <v>2.1549999999999998</v>
       </c>
-      <c r="D8" s="15"/>
-      <c r="E8" s="16" t="s">
+      <c r="D8" s="10"/>
+      <c r="E8" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10">
+        <f t="shared" si="0"/>
+        <v>0.69500000000000028</v>
+      </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="15">
+      <c r="A9" s="10">
         <v>31.2</v>
       </c>
-      <c r="B9" s="15"/>
-      <c r="C9" s="15">
+      <c r="B9" s="10"/>
+      <c r="C9" s="10">
         <v>2.1030000000000002</v>
       </c>
-      <c r="D9" s="15"/>
-      <c r="E9" s="16" t="s">
+      <c r="D9" s="10"/>
+      <c r="E9" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10">
+        <f t="shared" si="0"/>
+        <v>0.74699999999999989</v>
+      </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="15">
+      <c r="A10" s="10">
         <v>31.4</v>
       </c>
-      <c r="B10" s="15"/>
-      <c r="C10" s="15">
+      <c r="B10" s="10"/>
+      <c r="C10" s="10">
         <v>2.238</v>
       </c>
-      <c r="D10" s="15"/>
-      <c r="E10" s="16" t="s">
+      <c r="D10" s="10"/>
+      <c r="E10" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10">
+        <f t="shared" si="0"/>
+        <v>0.6120000000000001</v>
+      </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="15">
+      <c r="A11" s="10">
         <v>31.6</v>
       </c>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15">
+      <c r="B11" s="10"/>
+      <c r="C11" s="10">
         <v>2.3559999999999999</v>
       </c>
-      <c r="D11" s="15"/>
-      <c r="E11" s="16" t="s">
+      <c r="D11" s="10"/>
+      <c r="E11" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10">
+        <f t="shared" si="0"/>
+        <v>0.49400000000000022</v>
+      </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="15">
+      <c r="A12" s="10">
         <v>31.8</v>
       </c>
-      <c r="B12" s="15"/>
-      <c r="C12" s="15">
+      <c r="B12" s="10"/>
+      <c r="C12" s="10">
         <v>2.36</v>
       </c>
-      <c r="D12" s="15"/>
-      <c r="E12" s="16" t="s">
+      <c r="D12" s="10"/>
+      <c r="E12" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10">
+        <f t="shared" si="0"/>
+        <v>0.49000000000000021</v>
+      </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="15">
+      <c r="A13" s="10">
         <v>32</v>
       </c>
-      <c r="B13" s="15"/>
-      <c r="C13" s="15">
+      <c r="B13" s="10"/>
+      <c r="C13" s="10">
         <v>2.3010000000000002</v>
       </c>
-      <c r="D13" s="15"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10">
+        <f t="shared" si="0"/>
+        <v>0.54899999999999993</v>
+      </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="15">
+      <c r="A14" s="10">
         <v>32.200000000000003</v>
       </c>
-      <c r="B14" s="15"/>
-      <c r="C14" s="15">
+      <c r="B14" s="10"/>
+      <c r="C14" s="10">
         <v>2.2949999999999999</v>
       </c>
-      <c r="D14" s="15"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10">
+        <f t="shared" si="0"/>
+        <v>0.55500000000000016</v>
+      </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="15">
+      <c r="A15" s="10">
         <v>32.4</v>
       </c>
-      <c r="B15" s="15"/>
-      <c r="C15" s="15">
+      <c r="B15" s="10"/>
+      <c r="C15" s="10">
         <v>2.2839999999999998</v>
       </c>
-      <c r="D15" s="15"/>
-      <c r="E15" s="16" t="s">
+      <c r="D15" s="10"/>
+      <c r="E15" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10">
+        <f t="shared" si="0"/>
+        <v>0.56600000000000028</v>
+      </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="15">
+      <c r="A16" s="10">
         <v>32.6</v>
       </c>
-      <c r="B16" s="15"/>
-      <c r="C16" s="15">
+      <c r="B16" s="10"/>
+      <c r="C16" s="10">
         <v>2.25</v>
       </c>
-      <c r="D16" s="15"/>
-      <c r="E16" s="16" t="s">
+      <c r="D16" s="10"/>
+      <c r="E16" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10">
+        <f t="shared" si="0"/>
+        <v>0.60000000000000009</v>
+      </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="15">
+      <c r="A17" s="10">
         <v>32.799999999999997</v>
       </c>
-      <c r="B17" s="15"/>
-      <c r="C17" s="15">
+      <c r="B17" s="10"/>
+      <c r="C17" s="10">
         <v>2.3439999999999999</v>
       </c>
-      <c r="D17" s="15"/>
-      <c r="E17" s="16" t="s">
+      <c r="D17" s="10"/>
+      <c r="E17" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="F17" s="15"/>
-      <c r="G17" s="15"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10">
+        <f t="shared" si="0"/>
+        <v>0.50600000000000023</v>
+      </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="15">
+      <c r="A18" s="10">
         <v>33</v>
       </c>
-      <c r="B18" s="15"/>
-      <c r="C18" s="15">
+      <c r="B18" s="10"/>
+      <c r="C18" s="10">
         <v>2.34</v>
       </c>
-      <c r="D18" s="15"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="10">
+        <f t="shared" si="0"/>
+        <v>0.51000000000000023</v>
+      </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="15">
+      <c r="A19" s="10">
         <v>33.200000000000003</v>
       </c>
-      <c r="B19" s="15"/>
-      <c r="C19" s="15">
+      <c r="B19" s="10"/>
+      <c r="C19" s="10">
         <v>2.3450000000000002</v>
       </c>
-      <c r="D19" s="15"/>
-      <c r="E19" s="16" t="s">
+      <c r="D19" s="10"/>
+      <c r="E19" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="10">
+        <f t="shared" si="0"/>
+        <v>0.50499999999999989</v>
+      </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="15">
+      <c r="A20" s="10">
         <v>33.4</v>
       </c>
-      <c r="B20" s="15"/>
-      <c r="C20" s="15">
+      <c r="B20" s="10"/>
+      <c r="C20" s="10">
         <v>2.395</v>
       </c>
-      <c r="D20" s="15"/>
-      <c r="E20" s="16" t="s">
+      <c r="D20" s="10"/>
+      <c r="E20" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="10">
+        <f t="shared" si="0"/>
+        <v>0.45500000000000007</v>
+      </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="15">
+      <c r="A21" s="10">
         <v>33.6</v>
       </c>
-      <c r="B21" s="15"/>
-      <c r="C21" s="15">
+      <c r="B21" s="10"/>
+      <c r="C21" s="10">
         <v>2.4119999999999999</v>
       </c>
-      <c r="D21" s="15"/>
-      <c r="E21" s="16" t="s">
+      <c r="D21" s="10"/>
+      <c r="E21" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="10">
+        <f t="shared" si="0"/>
+        <v>0.43800000000000017</v>
+      </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="15">
+      <c r="A22" s="10">
         <v>33.799999999999997</v>
       </c>
-      <c r="B22" s="15"/>
-      <c r="C22" s="15">
+      <c r="B22" s="10"/>
+      <c r="C22" s="10">
         <v>2.46</v>
       </c>
-      <c r="D22" s="15"/>
-      <c r="E22" s="16" t="s">
+      <c r="D22" s="10"/>
+      <c r="E22" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="10">
+        <f t="shared" si="0"/>
+        <v>0.39000000000000012</v>
+      </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="15">
+      <c r="A23" s="10">
         <v>34</v>
       </c>
-      <c r="B23" s="15"/>
-      <c r="C23" s="15">
+      <c r="B23" s="10"/>
+      <c r="C23" s="10">
         <v>2.4300000000000002</v>
       </c>
-      <c r="D23" s="15"/>
-      <c r="E23" s="16" t="s">
+      <c r="D23" s="10"/>
+      <c r="E23" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="10">
+        <f t="shared" si="0"/>
+        <v>0.41999999999999993</v>
+      </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="15">
+      <c r="A24" s="10">
         <v>34.200000000000003</v>
       </c>
-      <c r="B24" s="15"/>
-      <c r="C24" s="15">
+      <c r="B24" s="10"/>
+      <c r="C24" s="10">
         <v>2.3180000000000001</v>
       </c>
-      <c r="D24" s="15"/>
-      <c r="E24" s="16" t="s">
+      <c r="D24" s="10"/>
+      <c r="E24" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F24" s="15"/>
-      <c r="G24" s="15"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="10">
+        <f t="shared" si="0"/>
+        <v>0.53200000000000003</v>
+      </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="15">
+      <c r="A25" s="10">
         <v>34.4</v>
       </c>
-      <c r="B25" s="15"/>
-      <c r="C25" s="15">
+      <c r="B25" s="10"/>
+      <c r="C25" s="10">
         <v>2.355</v>
       </c>
-      <c r="D25" s="15"/>
-      <c r="E25" s="16" t="s">
+      <c r="D25" s="10"/>
+      <c r="E25" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F25" s="15"/>
-      <c r="G25" s="15"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="10">
+        <f t="shared" si="0"/>
+        <v>0.49500000000000011</v>
+      </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="15">
+      <c r="A26" s="10">
         <v>34.6</v>
       </c>
-      <c r="B26" s="15"/>
-      <c r="C26" s="15">
+      <c r="B26" s="10"/>
+      <c r="C26" s="10">
         <v>2.4860000000000002</v>
       </c>
-      <c r="D26" s="15"/>
-      <c r="E26" s="16" t="s">
+      <c r="D26" s="10"/>
+      <c r="E26" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F26" s="15"/>
-      <c r="G26" s="15"/>
+      <c r="F26" s="10"/>
+      <c r="G26" s="10">
+        <f t="shared" si="0"/>
+        <v>0.36399999999999988</v>
+      </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="15">
+      <c r="A27" s="10">
         <v>34.799999999999997</v>
       </c>
-      <c r="B27" s="15"/>
-      <c r="C27" s="15">
+      <c r="B27" s="10"/>
+      <c r="C27" s="10">
         <v>2.516</v>
       </c>
-      <c r="D27" s="15"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="15"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="10"/>
+      <c r="G27" s="10">
+        <f t="shared" si="0"/>
+        <v>0.33400000000000007</v>
+      </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="15">
+      <c r="A28" s="10">
         <v>35</v>
       </c>
-      <c r="B28" s="15"/>
-      <c r="C28" s="15">
+      <c r="B28" s="10"/>
+      <c r="C28" s="10">
         <v>2.4550000000000001</v>
       </c>
-      <c r="D28" s="15"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="15"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="10">
+        <f t="shared" si="0"/>
+        <v>0.39500000000000002</v>
+      </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="15">
+      <c r="A29" s="10">
         <v>35.200000000000003</v>
       </c>
-      <c r="B29" s="15"/>
-      <c r="C29" s="15">
+      <c r="B29" s="10"/>
+      <c r="C29" s="10">
         <v>2.4470000000000001</v>
       </c>
-      <c r="D29" s="15"/>
-      <c r="E29" s="16" t="s">
+      <c r="D29" s="10"/>
+      <c r="E29" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="F29" s="15"/>
-      <c r="G29" s="15"/>
+      <c r="F29" s="10"/>
+      <c r="G29" s="10">
+        <f t="shared" si="0"/>
+        <v>0.40300000000000002</v>
+      </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="15">
+      <c r="A30" s="10">
         <v>35.4</v>
       </c>
-      <c r="B30" s="15"/>
-      <c r="C30" s="15">
+      <c r="B30" s="10"/>
+      <c r="C30" s="10">
         <v>2.4780000000000002</v>
       </c>
-      <c r="D30" s="15"/>
-      <c r="E30" s="16"/>
-      <c r="F30" s="15"/>
-      <c r="G30" s="15"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="10"/>
+      <c r="G30" s="10">
+        <f t="shared" si="0"/>
+        <v>0.37199999999999989</v>
+      </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="15">
+      <c r="A31" s="10">
         <v>35.6</v>
       </c>
-      <c r="B31" s="15"/>
-      <c r="C31" s="15">
+      <c r="B31" s="10"/>
+      <c r="C31" s="10">
         <v>2.4950000000000001</v>
       </c>
-      <c r="D31" s="15"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="15"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="10"/>
+      <c r="G31" s="10">
+        <f t="shared" si="0"/>
+        <v>0.35499999999999998</v>
+      </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="15">
+      <c r="A32" s="10">
         <v>35.799999999999997</v>
       </c>
-      <c r="B32" s="15"/>
-      <c r="C32" s="15">
+      <c r="B32" s="10"/>
+      <c r="C32" s="10">
         <v>2.4860000000000002</v>
       </c>
-      <c r="D32" s="15"/>
-      <c r="E32" s="16"/>
-      <c r="F32" s="15"/>
-      <c r="G32" s="15"/>
+      <c r="D32" s="10"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="10"/>
+      <c r="G32" s="10">
+        <f t="shared" si="0"/>
+        <v>0.36399999999999988</v>
+      </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="15">
+      <c r="A33" s="10">
         <v>36</v>
       </c>
-      <c r="B33" s="15"/>
-      <c r="C33" s="15">
+      <c r="B33" s="10"/>
+      <c r="C33" s="10">
         <v>2.512</v>
       </c>
-      <c r="D33" s="15"/>
-      <c r="E33" s="16" t="s">
+      <c r="D33" s="10"/>
+      <c r="E33" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="F33" s="15"/>
-      <c r="G33" s="15"/>
+      <c r="F33" s="10"/>
+      <c r="G33" s="10">
+        <f t="shared" si="0"/>
+        <v>0.33800000000000008</v>
+      </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="15">
+      <c r="A34" s="10">
         <v>36.200000000000003</v>
       </c>
-      <c r="B34" s="15"/>
-      <c r="C34" s="15">
+      <c r="B34" s="10"/>
+      <c r="C34" s="10">
         <v>2.5270000000000001</v>
       </c>
-      <c r="D34" s="15"/>
-      <c r="E34" s="16"/>
-      <c r="F34" s="15"/>
-      <c r="G34" s="15"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="10"/>
+      <c r="G34" s="10">
+        <f t="shared" si="0"/>
+        <v>0.32299999999999995</v>
+      </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="15">
+      <c r="A35" s="10">
         <v>36.4</v>
       </c>
-      <c r="B35" s="15"/>
-      <c r="C35" s="15">
+      <c r="B35" s="10"/>
+      <c r="C35" s="10">
         <v>2.552</v>
       </c>
-      <c r="D35" s="15"/>
-      <c r="E35" s="16"/>
-      <c r="F35" s="15"/>
-      <c r="G35" s="15"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="10"/>
+      <c r="G35" s="10">
+        <f t="shared" si="0"/>
+        <v>0.29800000000000004</v>
+      </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="15">
+      <c r="A36" s="10">
         <v>36.6</v>
       </c>
-      <c r="B36" s="15"/>
-      <c r="C36" s="15">
+      <c r="B36" s="10"/>
+      <c r="C36" s="10">
         <v>2.5659999999999998</v>
       </c>
-      <c r="D36" s="15"/>
-      <c r="E36" s="16" t="s">
+      <c r="D36" s="10"/>
+      <c r="E36" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="F36" s="15"/>
-      <c r="G36" s="15"/>
+      <c r="F36" s="10"/>
+      <c r="G36" s="10">
+        <f t="shared" si="0"/>
+        <v>0.28400000000000025</v>
+      </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="15">
+      <c r="A37" s="10">
         <v>36.799999999999997</v>
       </c>
-      <c r="B37" s="15"/>
-      <c r="C37" s="15">
+      <c r="B37" s="10"/>
+      <c r="C37" s="10">
         <v>2.6150000000000002</v>
       </c>
-      <c r="D37" s="15"/>
-      <c r="E37" s="16" t="s">
+      <c r="D37" s="10"/>
+      <c r="E37" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="F37" s="15"/>
-      <c r="G37" s="15"/>
+      <c r="F37" s="10"/>
+      <c r="G37" s="10">
+        <f t="shared" si="0"/>
+        <v>0.23499999999999988</v>
+      </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="15">
+      <c r="A38" s="10">
         <v>37</v>
       </c>
-      <c r="B38" s="15"/>
-      <c r="C38" s="15">
+      <c r="B38" s="10"/>
+      <c r="C38" s="10">
         <v>2.6850000000000001</v>
       </c>
-      <c r="D38" s="15"/>
-      <c r="E38" s="16" t="s">
+      <c r="D38" s="10"/>
+      <c r="E38" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="F38" s="15"/>
-      <c r="G38" s="15"/>
+      <c r="F38" s="10"/>
+      <c r="G38" s="10">
+        <f t="shared" si="0"/>
+        <v>0.16500000000000004</v>
+      </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="15">
+      <c r="A39" s="10">
         <v>37.200000000000003</v>
       </c>
-      <c r="B39" s="15"/>
-      <c r="C39" s="15">
+      <c r="B39" s="10"/>
+      <c r="C39" s="10">
         <v>2.6440000000000001</v>
       </c>
-      <c r="D39" s="15"/>
-      <c r="E39" s="16"/>
-      <c r="F39" s="15"/>
-      <c r="G39" s="15"/>
+      <c r="D39" s="10"/>
+      <c r="E39" s="13"/>
+      <c r="F39" s="10"/>
+      <c r="G39" s="10">
+        <f t="shared" si="0"/>
+        <v>0.20599999999999996</v>
+      </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="15">
+      <c r="A40" s="10">
         <v>37.4</v>
       </c>
-      <c r="B40" s="15"/>
-      <c r="C40" s="15">
+      <c r="B40" s="10"/>
+      <c r="C40" s="10">
         <v>2.7789999999999999</v>
       </c>
-      <c r="D40" s="15"/>
-      <c r="E40" s="16" t="s">
+      <c r="D40" s="10"/>
+      <c r="E40" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="F40" s="15"/>
-      <c r="G40" s="15"/>
+      <c r="F40" s="10"/>
+      <c r="G40" s="10">
+        <f t="shared" si="0"/>
+        <v>7.1000000000000174E-2</v>
+      </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="15">
+      <c r="A41" s="10">
         <v>37.6</v>
       </c>
-      <c r="B41" s="15"/>
-      <c r="C41" s="15">
+      <c r="B41" s="10"/>
+      <c r="C41" s="10">
         <v>2.806</v>
       </c>
-      <c r="D41" s="15"/>
-      <c r="E41" s="16" t="s">
+      <c r="D41" s="10"/>
+      <c r="E41" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="F41" s="15"/>
-      <c r="G41" s="15"/>
+      <c r="F41" s="10"/>
+      <c r="G41" s="10">
+        <f t="shared" si="0"/>
+        <v>4.4000000000000039E-2</v>
+      </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="15">
+      <c r="A42" s="10">
         <v>37.799999999999997</v>
       </c>
-      <c r="B42" s="15"/>
-      <c r="C42" s="15">
+      <c r="B42" s="10"/>
+      <c r="C42" s="10">
         <v>2.82</v>
       </c>
-      <c r="D42" s="15"/>
-      <c r="E42" s="16" t="s">
+      <c r="D42" s="10"/>
+      <c r="E42" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="F42" s="15"/>
-      <c r="G42" s="15"/>
+      <c r="F42" s="10"/>
+      <c r="G42" s="10">
+        <f t="shared" si="0"/>
+        <v>3.0000000000000249E-2</v>
+      </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="15">
+      <c r="A43" s="10">
         <v>38</v>
       </c>
-      <c r="B43" s="15"/>
-      <c r="C43" s="15">
+      <c r="B43" s="10"/>
+      <c r="C43" s="10">
         <v>2.7869999999999999</v>
       </c>
-      <c r="D43" s="15"/>
-      <c r="E43" s="16" t="s">
+      <c r="D43" s="10"/>
+      <c r="E43" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="F43" s="15"/>
-      <c r="G43" s="15"/>
+      <c r="F43" s="10"/>
+      <c r="G43" s="10">
+        <f t="shared" si="0"/>
+        <v>6.3000000000000167E-2</v>
+      </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="15">
+      <c r="A44" s="10">
         <v>38.200000000000003</v>
       </c>
-      <c r="B44" s="15"/>
-      <c r="C44" s="15">
+      <c r="B44" s="10"/>
+      <c r="C44" s="10">
         <v>2.78</v>
       </c>
-      <c r="D44" s="15"/>
-      <c r="E44" s="16" t="s">
+      <c r="D44" s="10"/>
+      <c r="E44" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="F44" s="15"/>
-      <c r="G44" s="15"/>
+      <c r="F44" s="10"/>
+      <c r="G44" s="10">
+        <f t="shared" si="0"/>
+        <v>7.0000000000000284E-2</v>
+      </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="15">
+      <c r="A45" s="10">
         <v>38.4</v>
       </c>
-      <c r="B45" s="15"/>
-      <c r="C45" s="15">
+      <c r="B45" s="10"/>
+      <c r="C45" s="10">
         <v>2.8159999999999998</v>
       </c>
-      <c r="D45" s="15"/>
-      <c r="E45" s="16" t="s">
+      <c r="D45" s="10"/>
+      <c r="E45" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="F45" s="15"/>
-      <c r="G45" s="15"/>
+      <c r="F45" s="10"/>
+      <c r="G45" s="10">
+        <f t="shared" si="0"/>
+        <v>3.4000000000000252E-2</v>
+      </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="15">
+      <c r="A46" s="10">
         <v>38.6</v>
       </c>
-      <c r="B46" s="15"/>
-      <c r="C46" s="15">
+      <c r="B46" s="10"/>
+      <c r="C46" s="10">
         <v>2.71</v>
       </c>
-      <c r="D46" s="15"/>
-      <c r="E46" s="16" t="s">
+      <c r="D46" s="10"/>
+      <c r="E46" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="F46" s="15"/>
-      <c r="G46" s="15"/>
+      <c r="F46" s="10"/>
+      <c r="G46" s="10">
+        <f t="shared" si="0"/>
+        <v>0.14000000000000012</v>
+      </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="15">
+      <c r="A47" s="10">
         <v>38.799999999999997</v>
       </c>
-      <c r="B47" s="15"/>
-      <c r="C47" s="15">
+      <c r="B47" s="10"/>
+      <c r="C47" s="10">
         <v>2.7629999999999999</v>
       </c>
-      <c r="D47" s="15"/>
-      <c r="E47" s="16"/>
-      <c r="F47" s="15"/>
-      <c r="G47" s="15"/>
+      <c r="D47" s="10"/>
+      <c r="E47" s="13"/>
+      <c r="F47" s="10"/>
+      <c r="G47" s="10">
+        <f t="shared" si="0"/>
+        <v>8.7000000000000188E-2</v>
+      </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="15">
+      <c r="A48" s="10">
         <v>39</v>
       </c>
-      <c r="B48" s="15"/>
-      <c r="C48" s="15">
+      <c r="B48" s="10"/>
+      <c r="C48" s="10">
         <v>2.8050000000000002</v>
       </c>
-      <c r="D48" s="15"/>
-      <c r="E48" s="16"/>
-      <c r="F48" s="15"/>
-      <c r="G48" s="15"/>
+      <c r="D48" s="10"/>
+      <c r="E48" s="13"/>
+      <c r="F48" s="10"/>
+      <c r="G48" s="10">
+        <f t="shared" si="0"/>
+        <v>4.4999999999999929E-2</v>
+      </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="15">
+      <c r="A49" s="10">
         <v>39.200000000000003</v>
       </c>
-      <c r="B49" s="15"/>
-      <c r="C49" s="15">
+      <c r="B49" s="10"/>
+      <c r="C49" s="10">
         <v>2.7850000000000001</v>
       </c>
-      <c r="D49" s="15"/>
-      <c r="E49" s="16"/>
-      <c r="F49" s="15"/>
-      <c r="G49" s="15"/>
+      <c r="D49" s="10"/>
+      <c r="E49" s="13"/>
+      <c r="F49" s="10"/>
+      <c r="G49" s="10">
+        <f t="shared" si="0"/>
+        <v>6.4999999999999947E-2</v>
+      </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="15">
+      <c r="A50" s="10">
         <v>39.4</v>
       </c>
-      <c r="B50" s="15"/>
-      <c r="C50" s="15">
+      <c r="B50" s="10"/>
+      <c r="C50" s="10">
         <v>2.802</v>
       </c>
-      <c r="D50" s="15"/>
-      <c r="E50" s="16"/>
-      <c r="F50" s="15"/>
-      <c r="G50" s="15"/>
+      <c r="D50" s="10"/>
+      <c r="E50" s="13"/>
+      <c r="F50" s="10"/>
+      <c r="G50" s="10">
+        <f t="shared" si="0"/>
+        <v>4.8000000000000043E-2</v>
+      </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="15">
+      <c r="A51" s="10">
         <v>39.6</v>
       </c>
-      <c r="B51" s="15"/>
-      <c r="C51" s="15">
+      <c r="B51" s="10"/>
+      <c r="C51" s="10">
         <v>2.81</v>
       </c>
-      <c r="D51" s="15"/>
-      <c r="E51" s="16" t="s">
+      <c r="D51" s="10"/>
+      <c r="E51" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="F51" s="15"/>
-      <c r="G51" s="15"/>
+      <c r="F51" s="10"/>
+      <c r="G51" s="10">
+        <f t="shared" si="0"/>
+        <v>4.0000000000000036E-2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -1610,25 +4228,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="21">
+      <c r="B1" s="18">
         <v>0.61805555555555558</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="22">
+      <c r="D1" s="19">
         <v>0.62361111111111112</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
@@ -1646,310 +4264,310 @@
       <c r="E2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="23" t="s">
+      <c r="F2" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="G2" s="24" t="s">
+      <c r="G2" s="21" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="25">
+      <c r="A3" s="11">
         <v>0</v>
       </c>
-      <c r="B3" s="25">
+      <c r="B3" s="11">
         <v>2.036</v>
       </c>
-      <c r="C3" s="25" t="s">
+      <c r="C3" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="25"/>
-      <c r="E3" s="25" t="s">
+      <c r="D3" s="11"/>
+      <c r="E3" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="F3" s="25"/>
-      <c r="G3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="9"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="12">
+      <c r="A4" s="10">
         <v>10</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12">
+      <c r="B4" s="10"/>
+      <c r="C4" s="10">
         <v>2.093</v>
       </c>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12" t="s">
+      <c r="D4" s="10"/>
+      <c r="E4" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="12"/>
+      <c r="F4" s="10"/>
       <c r="G4" s="1"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="12">
+      <c r="A5" s="10">
         <v>20</v>
       </c>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12">
+      <c r="B5" s="10"/>
+      <c r="C5" s="10">
         <v>2.286</v>
       </c>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12" t="s">
+      <c r="D5" s="10"/>
+      <c r="E5" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="F5" s="12"/>
+      <c r="F5" s="10"/>
       <c r="G5" s="1"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="12">
+      <c r="A6" s="10">
         <v>30</v>
       </c>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12">
+      <c r="B6" s="10"/>
+      <c r="C6" s="10">
         <v>2.3140000000000001</v>
       </c>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12" t="s">
+      <c r="D6" s="10"/>
+      <c r="E6" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="12"/>
+      <c r="F6" s="10"/>
       <c r="G6" s="1"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="12">
+      <c r="A7" s="10">
         <v>40</v>
       </c>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12">
+      <c r="B7" s="10"/>
+      <c r="C7" s="10">
         <v>2.3239999999999998</v>
       </c>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12" t="s">
+      <c r="D7" s="10"/>
+      <c r="E7" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F7" s="12"/>
+      <c r="F7" s="10"/>
       <c r="G7" s="1"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="12">
+      <c r="A8" s="10">
         <v>50</v>
       </c>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12">
+      <c r="B8" s="10"/>
+      <c r="C8" s="10">
         <v>2.3490000000000002</v>
       </c>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12" t="s">
+      <c r="D8" s="10"/>
+      <c r="E8" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="F8" s="12"/>
+      <c r="F8" s="10"/>
       <c r="G8" s="1"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="12">
+      <c r="A9" s="10">
         <v>60</v>
       </c>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12">
+      <c r="B9" s="10"/>
+      <c r="C9" s="10">
         <v>2.415</v>
       </c>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
       <c r="G9" s="1"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="12">
+      <c r="A10" s="10">
         <v>70</v>
       </c>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12">
+      <c r="B10" s="10"/>
+      <c r="C10" s="10">
         <v>2.4209999999999998</v>
       </c>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
       <c r="G10" s="1"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="12">
+      <c r="A11" s="10">
         <v>80</v>
       </c>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12">
+      <c r="B11" s="10"/>
+      <c r="C11" s="10">
         <v>2.4249999999999998</v>
       </c>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12" t="s">
+      <c r="D11" s="10"/>
+      <c r="E11" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="F11" s="12"/>
+      <c r="F11" s="10"/>
       <c r="G11" s="1"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="12">
+      <c r="A12" s="10">
         <v>90</v>
       </c>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12">
+      <c r="B12" s="10"/>
+      <c r="C12" s="10">
         <v>2.3490000000000002</v>
       </c>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12" t="s">
+      <c r="D12" s="10"/>
+      <c r="E12" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="F12" s="12"/>
+      <c r="F12" s="10"/>
       <c r="G12" s="1"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="12">
+      <c r="A13" s="10">
         <v>100</v>
       </c>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12">
+      <c r="B13" s="10"/>
+      <c r="C13" s="10">
         <v>2.33</v>
       </c>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12" t="s">
+      <c r="D13" s="10"/>
+      <c r="E13" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="F13" s="12"/>
+      <c r="F13" s="10"/>
       <c r="G13" s="1"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="12">
+      <c r="A14" s="10">
         <v>110</v>
       </c>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12">
+      <c r="B14" s="10"/>
+      <c r="C14" s="10">
         <v>2.3410000000000002</v>
       </c>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
       <c r="G14" s="1"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="12">
+      <c r="A15" s="10">
         <v>120</v>
       </c>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12">
+      <c r="B15" s="10"/>
+      <c r="C15" s="10">
         <v>2.42</v>
       </c>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12" t="s">
+      <c r="D15" s="10"/>
+      <c r="E15" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="F15" s="12"/>
+      <c r="F15" s="10"/>
       <c r="G15" s="1"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="12">
+      <c r="A16" s="10">
         <v>130</v>
       </c>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12">
+      <c r="B16" s="10"/>
+      <c r="C16" s="10">
         <v>2.39</v>
       </c>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
       <c r="G16" s="1"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="12">
+      <c r="A17" s="10">
         <v>140</v>
       </c>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12">
+      <c r="B17" s="10"/>
+      <c r="C17" s="10">
         <v>2.407</v>
       </c>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
       <c r="G17" s="1"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="12">
+      <c r="A18" s="10">
         <v>150</v>
       </c>
-      <c r="B18" s="12"/>
-      <c r="C18" s="12">
+      <c r="B18" s="10"/>
+      <c r="C18" s="10">
         <v>2.3250000000000002</v>
       </c>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="10"/>
       <c r="G18" s="1"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="12">
+      <c r="A19" s="10">
         <v>160</v>
       </c>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12">
+      <c r="B19" s="10"/>
+      <c r="C19" s="10">
         <v>2.3290000000000002</v>
       </c>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12" t="s">
+      <c r="D19" s="10"/>
+      <c r="E19" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="F19" s="12"/>
+      <c r="F19" s="10"/>
       <c r="G19" s="1"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="12">
+      <c r="A20" s="10">
         <v>170</v>
       </c>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12">
+      <c r="B20" s="10"/>
+      <c r="C20" s="10">
         <v>2.2650000000000001</v>
       </c>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="10"/>
       <c r="G20" s="1"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="12">
+      <c r="A21" s="10">
         <v>180</v>
       </c>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12">
+      <c r="B21" s="10"/>
+      <c r="C21" s="10">
         <v>2.238</v>
       </c>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="10"/>
       <c r="G21" s="1"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="12">
+      <c r="A22" s="10">
         <v>190</v>
       </c>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12">
+      <c r="B22" s="10"/>
+      <c r="C22" s="10">
         <v>2.0430000000000001</v>
       </c>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12" t="s">
+      <c r="D22" s="10"/>
+      <c r="E22" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="F22" s="12"/>
+      <c r="F22" s="10"/>
       <c r="G22" s="1"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="12">
+      <c r="A23" s="10">
         <v>200</v>
       </c>
-      <c r="B23" s="12"/>
-      <c r="C23" s="12">
+      <c r="B23" s="10"/>
+      <c r="C23" s="10">
         <v>2.0259999999999998</v>
       </c>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="10"/>
       <c r="G23" s="1"/>
     </row>
     <row r="35" spans="7:7" x14ac:dyDescent="0.25">
@@ -2022,7 +4640,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89726CEA-630F-48B7-8156-202D59EF07D9}">
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:P39"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.7109375" customWidth="1"/>
@@ -2037,13 +4655,13 @@
       <c r="A1" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="31">
+      <c r="B1" s="25">
         <v>0.12708333333333333</v>
       </c>
-      <c r="C1" s="32" t="s">
+      <c r="C1" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="D1" s="33">
+      <c r="D1" s="26">
         <v>0.13541666666666666</v>
       </c>
       <c r="E1" s="5" t="s">
@@ -2065,466 +4683,640 @@
       <c r="D2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="26" t="s">
+      <c r="F2" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="G2" s="27" t="s">
+      <c r="G2" s="4" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="12">
+      <c r="A3" s="10">
         <v>0</v>
       </c>
-      <c r="B3" s="12">
+      <c r="B3" s="10">
         <v>1.9430000000000001</v>
       </c>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12" t="s">
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F3" s="25"/>
-      <c r="G3" s="25"/>
+      <c r="F3" s="11">
+        <f>B3+G3</f>
+        <v>2757.9430000000002</v>
+      </c>
+      <c r="G3" s="11">
+        <v>2756</v>
+      </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="12">
+      <c r="A4" s="10">
         <v>10</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12">
+      <c r="B4" s="10"/>
+      <c r="C4" s="10">
         <v>1.964</v>
       </c>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10">
+        <f>$F$3-C4</f>
+        <v>2755.9790000000003</v>
+      </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="12">
+      <c r="A5" s="10">
         <v>20</v>
       </c>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12">
+      <c r="B5" s="10"/>
+      <c r="C5" s="10">
         <v>1.9419999999999999</v>
       </c>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12" t="s">
+      <c r="D5" s="10"/>
+      <c r="E5" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10">
+        <f>$F$3-C5</f>
+        <v>2756.0010000000002</v>
+      </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="12">
+      <c r="A6" s="10">
         <v>30</v>
       </c>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12">
+      <c r="B6" s="10"/>
+      <c r="C6" s="10">
         <v>2.0209999999999999</v>
       </c>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12" t="s">
+      <c r="D6" s="10"/>
+      <c r="E6" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10">
+        <f t="shared" ref="G6:G33" si="0">$F$3-C6</f>
+        <v>2755.922</v>
+      </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="12">
+      <c r="A7" s="10">
         <v>40</v>
       </c>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12">
+      <c r="B7" s="10"/>
+      <c r="C7" s="10">
         <v>2.0630000000000002</v>
       </c>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10">
+        <f t="shared" si="0"/>
+        <v>2755.88</v>
+      </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="12">
+      <c r="A8" s="10">
         <v>50</v>
       </c>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12">
+      <c r="B8" s="10"/>
+      <c r="C8" s="10">
         <v>2.15</v>
       </c>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12" t="s">
+      <c r="D8" s="10"/>
+      <c r="E8" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10">
+        <f t="shared" si="0"/>
+        <v>2755.7930000000001</v>
+      </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="12">
+      <c r="A9" s="10">
         <v>60</v>
       </c>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12">
+      <c r="B9" s="10"/>
+      <c r="C9" s="10">
         <v>2.2029999999999998</v>
       </c>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12" t="s">
+      <c r="D9" s="10"/>
+      <c r="E9" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10">
+        <f t="shared" si="0"/>
+        <v>2755.7400000000002</v>
+      </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="12">
+      <c r="A10" s="10">
         <v>70</v>
       </c>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12">
+      <c r="B10" s="10"/>
+      <c r="C10" s="10">
         <v>2.2930000000000001</v>
       </c>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12" t="s">
+      <c r="D10" s="10"/>
+      <c r="E10" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10">
+        <f t="shared" si="0"/>
+        <v>2755.65</v>
+      </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="12">
+      <c r="A11" s="10">
         <v>80</v>
       </c>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12">
+      <c r="B11" s="10"/>
+      <c r="C11" s="10">
         <v>2.3199999999999998</v>
       </c>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10">
+        <f t="shared" si="0"/>
+        <v>2755.623</v>
+      </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="12">
+      <c r="A12" s="10">
         <v>90</v>
       </c>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12">
+      <c r="B12" s="10"/>
+      <c r="C12" s="10">
         <v>2.3149999999999999</v>
       </c>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10">
+        <f t="shared" si="0"/>
+        <v>2755.6280000000002</v>
+      </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="12">
+      <c r="A13" s="10">
         <v>100</v>
       </c>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12">
+      <c r="B13" s="10"/>
+      <c r="C13" s="10">
         <v>2.4159999999999999</v>
       </c>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12" t="s">
+      <c r="D13" s="10"/>
+      <c r="E13" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10">
+        <f t="shared" si="0"/>
+        <v>2755.527</v>
+      </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="12">
+      <c r="A14" s="10">
         <v>110</v>
       </c>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12">
+      <c r="B14" s="10"/>
+      <c r="C14" s="10">
         <v>2.4470000000000001</v>
       </c>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10">
+        <f t="shared" si="0"/>
+        <v>2755.4960000000001</v>
+      </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="12">
+      <c r="A15" s="10">
         <v>120</v>
       </c>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12">
+      <c r="B15" s="10"/>
+      <c r="C15" s="10">
         <v>2.46</v>
       </c>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10">
+        <f t="shared" si="0"/>
+        <v>2755.4830000000002</v>
+      </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="12">
+      <c r="A16" s="10">
         <v>130</v>
       </c>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12">
+      <c r="B16" s="10"/>
+      <c r="C16" s="10">
         <v>2.456</v>
       </c>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12" t="s">
+      <c r="D16" s="10"/>
+      <c r="E16" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="12">
+      <c r="F16" s="10"/>
+      <c r="G16" s="10">
+        <f t="shared" si="0"/>
+        <v>2755.4870000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A17" s="10">
         <v>140</v>
       </c>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12">
+      <c r="B17" s="10"/>
+      <c r="C17" s="10">
         <v>2.496</v>
       </c>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12" t="s">
+      <c r="D17" s="10"/>
+      <c r="E17" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="12">
+      <c r="F17" s="10"/>
+      <c r="G17" s="10">
+        <f t="shared" si="0"/>
+        <v>2755.4470000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A18" s="10">
         <v>150</v>
       </c>
-      <c r="B18" s="12"/>
-      <c r="C18" s="12">
+      <c r="B18" s="10"/>
+      <c r="C18" s="10">
         <v>2.46</v>
       </c>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12" t="s">
+      <c r="D18" s="10"/>
+      <c r="E18" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="12">
+      <c r="F18" s="10"/>
+      <c r="G18" s="10">
+        <f t="shared" si="0"/>
+        <v>2755.4830000000002</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A19" s="10">
         <v>160</v>
       </c>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12">
+      <c r="B19" s="10"/>
+      <c r="C19" s="10">
         <v>2.5099999999999998</v>
       </c>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12" t="s">
+      <c r="D19" s="10"/>
+      <c r="E19" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="12">
+      <c r="F19" s="10"/>
+      <c r="G19" s="10">
+        <f t="shared" si="0"/>
+        <v>2755.433</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A20" s="10">
         <v>170</v>
       </c>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12">
+      <c r="B20" s="10"/>
+      <c r="C20" s="10">
         <v>2.4830000000000001</v>
       </c>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12" t="s">
+      <c r="D20" s="10"/>
+      <c r="E20" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="12">
+      <c r="F20" s="10"/>
+      <c r="G20" s="10">
+        <f t="shared" si="0"/>
+        <v>2755.46</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A21" s="10">
         <v>180</v>
       </c>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12">
+      <c r="B21" s="10"/>
+      <c r="C21" s="10">
         <v>2.4750000000000001</v>
       </c>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="12">
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="10">
+        <f t="shared" si="0"/>
+        <v>2755.4680000000003</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A22" s="10">
         <v>190</v>
       </c>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12">
+      <c r="B22" s="10"/>
+      <c r="C22" s="10">
         <v>2.4289999999999998</v>
       </c>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12" t="s">
+      <c r="D22" s="10"/>
+      <c r="E22" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="12">
+      <c r="F22" s="10"/>
+      <c r="G22" s="10">
+        <f t="shared" si="0"/>
+        <v>2755.5140000000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A23" s="10">
         <v>200</v>
       </c>
-      <c r="B23" s="12"/>
-      <c r="C23" s="12">
+      <c r="B23" s="10"/>
+      <c r="C23" s="10">
         <v>2.4249999999999998</v>
       </c>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="12">
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="10">
+        <f t="shared" si="0"/>
+        <v>2755.518</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A24" s="10">
         <v>210</v>
       </c>
-      <c r="B24" s="12"/>
-      <c r="C24" s="12">
+      <c r="B24" s="10"/>
+      <c r="C24" s="10">
         <v>2.42</v>
       </c>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="12"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="12">
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="10">
+        <f t="shared" si="0"/>
+        <v>2755.5230000000001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A25" s="10">
         <v>220</v>
       </c>
-      <c r="B25" s="12"/>
-      <c r="C25" s="12">
+      <c r="B25" s="10"/>
+      <c r="C25" s="10">
         <v>2.3969999999999998</v>
       </c>
-      <c r="D25" s="12"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="12"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="12">
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="10">
+        <f t="shared" si="0"/>
+        <v>2755.5460000000003</v>
+      </c>
+      <c r="I25" s="10">
+        <v>100</v>
+      </c>
+      <c r="J25" s="10">
+        <f>G13</f>
+        <v>2755.527</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A26" s="10">
         <v>230</v>
       </c>
-      <c r="B26" s="12"/>
-      <c r="C26" s="34">
+      <c r="B26" s="10"/>
+      <c r="C26" s="27">
         <v>2.4079999999999999</v>
       </c>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12" t="s">
+      <c r="D26" s="10"/>
+      <c r="E26" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="F26" s="12"/>
-      <c r="G26" s="12"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="12">
+      <c r="F26" s="10"/>
+      <c r="G26" s="10">
+        <f t="shared" si="0"/>
+        <v>2755.5350000000003</v>
+      </c>
+      <c r="I26" s="10">
+        <v>120</v>
+      </c>
+      <c r="J26" s="10">
+        <f>J25+0.001</f>
+        <v>2755.5280000000002</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A27" s="10">
         <v>240</v>
       </c>
-      <c r="B27" s="12"/>
-      <c r="C27" s="12">
+      <c r="B27" s="10"/>
+      <c r="C27" s="10">
         <v>2.3780000000000001</v>
       </c>
-      <c r="D27" s="12"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="12"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="12">
+      <c r="D27" s="10"/>
+      <c r="E27" s="10"/>
+      <c r="F27" s="10"/>
+      <c r="G27" s="10">
+        <f t="shared" si="0"/>
+        <v>2755.5650000000001</v>
+      </c>
+      <c r="I27" s="28">
+        <v>130</v>
+      </c>
+      <c r="J27" s="28">
+        <f t="shared" ref="J27:J30" si="1">J26+0.001</f>
+        <v>2755.5290000000005</v>
+      </c>
+      <c r="L27" t="s">
+        <v>56</v>
+      </c>
+      <c r="O27" s="29">
+        <f>J27-G16</f>
+        <v>4.2000000000371074E-2</v>
+      </c>
+      <c r="P27" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A28" s="10">
         <v>250</v>
       </c>
-      <c r="B28" s="12"/>
-      <c r="C28" s="12">
+      <c r="B28" s="10"/>
+      <c r="C28" s="10">
         <v>2.3570000000000002</v>
       </c>
-      <c r="D28" s="12"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="12"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="12">
+      <c r="D28" s="10"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="10">
+        <f t="shared" si="0"/>
+        <v>2755.5860000000002</v>
+      </c>
+      <c r="I28" s="10">
+        <v>150</v>
+      </c>
+      <c r="J28" s="10">
+        <f t="shared" si="1"/>
+        <v>2755.5300000000007</v>
+      </c>
+      <c r="O28" s="5">
+        <f>O27*100</f>
+        <v>4.2000000000371074</v>
+      </c>
+      <c r="P28" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A29" s="10">
         <v>260</v>
       </c>
-      <c r="B29" s="12"/>
-      <c r="C29" s="12">
+      <c r="B29" s="10"/>
+      <c r="C29" s="10">
         <v>2.3450000000000002</v>
       </c>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="12"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="12">
+      <c r="D29" s="10"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="10"/>
+      <c r="G29" s="10">
+        <f t="shared" si="0"/>
+        <v>2755.5980000000004</v>
+      </c>
+      <c r="I29" s="10">
+        <v>170</v>
+      </c>
+      <c r="J29" s="10">
+        <f t="shared" si="1"/>
+        <v>2755.5310000000009</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A30" s="10">
         <v>270</v>
       </c>
-      <c r="B30" s="12"/>
-      <c r="C30" s="12">
+      <c r="B30" s="10"/>
+      <c r="C30" s="10">
         <v>2.34</v>
       </c>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="12"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="12">
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="10"/>
+      <c r="G30" s="10">
+        <f t="shared" si="0"/>
+        <v>2755.6030000000001</v>
+      </c>
+      <c r="I30" s="10">
+        <v>200</v>
+      </c>
+      <c r="J30" s="10">
+        <f t="shared" si="1"/>
+        <v>2755.5320000000011</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A31" s="10">
         <v>280</v>
       </c>
-      <c r="B31" s="12"/>
-      <c r="C31" s="12">
+      <c r="B31" s="10"/>
+      <c r="C31" s="10">
         <v>2.327</v>
       </c>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="12"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="12">
+      <c r="D31" s="10"/>
+      <c r="E31" s="10"/>
+      <c r="F31" s="10"/>
+      <c r="G31" s="10">
+        <f t="shared" si="0"/>
+        <v>2755.616</v>
+      </c>
+      <c r="I31" s="10">
+        <v>230</v>
+      </c>
+      <c r="J31" s="10">
+        <f>G26</f>
+        <v>2755.5350000000003</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A32" s="10">
         <v>290</v>
       </c>
-      <c r="B32" s="12"/>
-      <c r="C32" s="12">
+      <c r="B32" s="10"/>
+      <c r="C32" s="10">
         <v>2.1859999999999999</v>
       </c>
-      <c r="D32" s="12"/>
-      <c r="E32" s="12" t="s">
+      <c r="D32" s="10"/>
+      <c r="E32" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="F32" s="12"/>
-      <c r="G32" s="12"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="12">
+      <c r="F32" s="10"/>
+      <c r="G32" s="10">
+        <f t="shared" si="0"/>
+        <v>2755.7570000000001</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="10">
         <v>300</v>
       </c>
-      <c r="B33" s="12"/>
-      <c r="C33" s="12">
+      <c r="B33" s="10"/>
+      <c r="C33" s="10">
         <v>2.15</v>
       </c>
-      <c r="D33" s="12"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="12"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="12">
+      <c r="D33" s="10"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="10"/>
+      <c r="G33" s="10">
+        <f t="shared" si="0"/>
+        <v>2755.7930000000001</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="10">
         <v>310</v>
       </c>
-      <c r="B34" s="12"/>
-      <c r="C34" s="12">
+      <c r="B34" s="10"/>
+      <c r="C34" s="10">
         <v>2.06</v>
       </c>
-      <c r="D34" s="12"/>
-      <c r="E34" s="12" t="s">
+      <c r="D34" s="10"/>
+      <c r="E34" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="F34" s="12"/>
-      <c r="G34" s="12"/>
+      <c r="F34" s="10"/>
+      <c r="G34" s="10">
+        <f>$F$3-C34</f>
+        <v>2755.8830000000003</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I39" s="10">
+        <v>2755.4870000000001</v>
+      </c>
+      <c r="J39">
+        <f>I39+0.114</f>
+        <v>2755.6010000000001</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2540,19 +5332,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="28">
+      <c r="B1" s="22">
         <v>0.1423611111111111</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="29">
+      <c r="D1" s="23">
         <v>0.14722222222222223</v>
       </c>
-      <c r="E1" s="30" t="s">
+      <c r="E1" s="24" t="s">
         <v>43</v>
       </c>
     </row>
@@ -2574,212 +5366,212 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="12">
+      <c r="A3" s="10">
         <v>0</v>
       </c>
-      <c r="B3" s="12">
+      <c r="B3" s="10">
         <v>1.9</v>
       </c>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12" t="s">
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="12">
+      <c r="A4" s="10">
         <v>10</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12">
+      <c r="B4" s="10"/>
+      <c r="C4" s="10">
         <v>1.895</v>
       </c>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="12">
+      <c r="A5" s="10">
         <v>20</v>
       </c>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12">
+      <c r="B5" s="10"/>
+      <c r="C5" s="10">
         <v>1.9770000000000001</v>
       </c>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12" t="s">
+      <c r="D5" s="10"/>
+      <c r="E5" s="10" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="12">
+      <c r="A6" s="10">
         <v>30</v>
       </c>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12">
+      <c r="B6" s="10"/>
+      <c r="C6" s="10">
         <v>2.11</v>
       </c>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12" t="s">
+      <c r="D6" s="10"/>
+      <c r="E6" s="10" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="12">
+      <c r="A7" s="10">
         <v>40</v>
       </c>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12">
+      <c r="B7" s="10"/>
+      <c r="C7" s="10">
         <v>2.14</v>
       </c>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12" t="s">
+      <c r="D7" s="10"/>
+      <c r="E7" s="10" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="12">
+      <c r="A8" s="10">
         <v>50</v>
       </c>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12">
+      <c r="B8" s="10"/>
+      <c r="C8" s="10">
         <v>2.1909999999999998</v>
       </c>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="12">
+      <c r="A9" s="10">
         <v>60</v>
       </c>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12">
+      <c r="B9" s="10"/>
+      <c r="C9" s="10">
         <v>2.2599999999999998</v>
       </c>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="12">
+      <c r="A10" s="10">
         <v>70</v>
       </c>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12">
+      <c r="B10" s="10"/>
+      <c r="C10" s="10">
         <v>2.2749999999999999</v>
       </c>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="12">
+      <c r="A11" s="10">
         <v>80</v>
       </c>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12">
+      <c r="B11" s="10"/>
+      <c r="C11" s="10">
         <v>2.2799999999999998</v>
       </c>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="12">
+      <c r="A12" s="10">
         <v>90</v>
       </c>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12">
+      <c r="B12" s="10"/>
+      <c r="C12" s="10">
         <v>2.2949999999999999</v>
       </c>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="12">
+      <c r="A13" s="10">
         <v>100</v>
       </c>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12">
+      <c r="B13" s="10"/>
+      <c r="C13" s="10">
         <v>2.282</v>
       </c>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="12">
+      <c r="A14" s="10">
         <v>110</v>
       </c>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12">
+      <c r="B14" s="10"/>
+      <c r="C14" s="10">
         <v>2.2650000000000001</v>
       </c>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="12">
+      <c r="A15" s="10">
         <v>120</v>
       </c>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12">
+      <c r="B15" s="10"/>
+      <c r="C15" s="10">
         <v>2.274</v>
       </c>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="12">
+      <c r="A16" s="10">
         <v>130</v>
       </c>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12">
+      <c r="B16" s="10"/>
+      <c r="C16" s="10">
         <v>2.2759999999999998</v>
       </c>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12" t="s">
+      <c r="D16" s="10"/>
+      <c r="E16" s="10" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="12">
+      <c r="A17" s="10">
         <v>140</v>
       </c>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12">
+      <c r="B17" s="10"/>
+      <c r="C17" s="10">
         <v>2.1520000000000001</v>
       </c>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="12">
+      <c r="A18" s="10">
         <v>150</v>
       </c>
-      <c r="B18" s="12"/>
-      <c r="C18" s="12">
+      <c r="B18" s="10"/>
+      <c r="C18" s="10">
         <v>2.1280000000000001</v>
       </c>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="12">
+      <c r="A19" s="10">
         <v>160</v>
       </c>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12">
+      <c r="B19" s="10"/>
+      <c r="C19" s="10">
         <v>2.09</v>
       </c>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="12">
+      <c r="A20" s="10">
         <v>170</v>
       </c>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12">
+      <c r="B20" s="10"/>
+      <c r="C20" s="10">
         <v>2.0870000000000002</v>
       </c>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
